--- a/Reinfection_Augments_Heterogeneity/Public/Final Dataframes/Metadata_prior_pathogen_exposure_augments_inter-individual_heterogeneity.xlsx
+++ b/Reinfection_Augments_Heterogeneity/Public/Final Dataframes/Metadata_prior_pathogen_exposure_augments_inter-individual_heterogeneity.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jesse/Documents/GitHub/EEID_1A_Mechanistic_Link/Reinfection_Augments_Heterogeneity/Public/Final Dataframes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{966B9537-057F-7342-BF5B-7C977B082EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC32729-73E4-344A-AB7C-F67B035A8F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="1080" windowWidth="27640" windowHeight="15220" activeTab="2" xr2:uid="{EC738A6A-93A8-404E-A8DD-1ABD73873546}"/>
+    <workbookView xWindow="280" yWindow="920" windowWidth="27660" windowHeight="15240" activeTab="4" xr2:uid="{EC738A6A-93A8-404E-A8DD-1ABD73873546}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Data" sheetId="1" r:id="rId1"/>
     <sheet name="EEID_1a_ELISA" sheetId="2" r:id="rId2"/>
     <sheet name="Reinfection Response" sheetId="3" r:id="rId3"/>
+    <sheet name="all_pseudosets" sheetId="4" r:id="rId4"/>
+    <sheet name="deviance_params_noday41positive" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="199">
   <si>
     <t>Variable</t>
   </si>
@@ -575,16 +577,83 @@
   </si>
   <si>
     <t>Whether an individual bird was infected or not (pathogen load &gt; 50) on a given day during the experiment</t>
+  </si>
+  <si>
+    <t>Each row represents ond of 1,000 bootstrapped pseudoreplicates from the dose-response model fits per prior exposure group</t>
+  </si>
+  <si>
+    <t>par1.gamma</t>
+  </si>
+  <si>
+    <t>par2.gamma</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>bird.groups</t>
+  </si>
+  <si>
+    <t>counter</t>
+  </si>
+  <si>
+    <t>Shape parameter of fitted gamma susceptiblity distribution for this pseudoreplicate</t>
+  </si>
+  <si>
+    <t>Scale parameter for fitted gamma susceptibility distribution for this pseudoreplicate</t>
+  </si>
+  <si>
+    <t>Exposure group with pseudoreplicate index</t>
+  </si>
+  <si>
+    <t>Prior exposure group (CCU/mL)</t>
+  </si>
+  <si>
+    <t>Psuedoreplicate index</t>
+  </si>
+  <si>
+    <t>30000, 750, or 0 with "va_" followed by a number between 1 and 1000</t>
+  </si>
+  <si>
+    <t>30000, 750, or 0 with "va" appended</t>
+  </si>
+  <si>
+    <t>positive number beteen 1 and 1000</t>
+  </si>
+  <si>
+    <t>Shape parameter for the best-fit gamma susceptiblity distribution</t>
+  </si>
+  <si>
+    <t>Scale parameter for the best-fit gamma susceptibility distribution</t>
+  </si>
+  <si>
+    <t>Prior exposure group</t>
+  </si>
+  <si>
+    <t>Observed best-fit dose-response parameters for each prior exposure group</t>
+  </si>
+  <si>
+    <t>positive value</t>
+  </si>
+  <si>
+    <t>30000 va, 750 va, or 0 va</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -610,10 +679,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2375,4 +2445,154 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{258547E0-54AB-4644-87B6-1AACEF00D9C9}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A0D47CF-D825-C54C-9CCA-D769CF57A04A}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="54.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>